--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487775_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487775_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. TREVIÑO QUINTILLÁ</t>
+          <t>D. ORRIT SERRANO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.869</v>
+        <v>9.8764</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7427</v>
+        <v>6.0579</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1263</v>
+        <v>3.8185</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1758</v>
+        <v>2.3742</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5373</v>
+        <v>-0.9086</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7131</v>
+        <v>3.2828</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9514</v>
+        <v>1.7826</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0472</v>
+        <v>-0.4634</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9986</v>
+        <v>2.246</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2244</v>
+        <v>0.5917</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4901</v>
+        <v>-0.4452</v>
       </c>
       <c r="O2" t="n">
-        <v>1.7145</v>
+        <v>1.0369</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1218</v>
+        <v>2.7055</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7774</v>
+        <v>1.1672</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7237</v>
+        <v>0.6458</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0537</v>
+        <v>0.5213</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8751</v>
+        <v>4.6701</v>
       </c>
       <c r="W2" t="n">
-        <v>3.1488</v>
+        <v>4.6701</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. ORRIT SERRANO</t>
+          <t>P. TREVIÑO QUINTILLÁ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.4948</v>
+        <v>7.5585</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0579</v>
+        <v>3.8139</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4368</v>
+        <v>3.7446</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3742</v>
+        <v>3.1758</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9086</v>
+        <v>-0.5373</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2828</v>
+        <v>3.7131</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7826</v>
+        <v>1.9514</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4634</v>
+        <v>-0.0472</v>
       </c>
       <c r="L3" t="n">
-        <v>2.246</v>
+        <v>1.9986</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5917</v>
+        <v>1.2244</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4452</v>
+        <v>-0.4901</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0369</v>
+        <v>1.7145</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7055</v>
+        <v>3.1218</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7855</v>
+        <v>1.4669</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6458</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1397</v>
+        <v>0.672</v>
       </c>
       <c r="V3" t="n">
-        <v>4.6701</v>
+        <v>1.8751</v>
       </c>
       <c r="W3" t="n">
-        <v>4.6701</v>
+        <v>3.1488</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.2737</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.867</v>
+        <v>5.9591</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1693</v>
+        <v>3.0266</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6977</v>
+        <v>2.9325</v>
       </c>
       <c r="G4" t="n">
         <v>3.7843</v>
@@ -766,13 +766,13 @@
         <v>2.9137</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6635</v>
+        <v>0.4286</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9663</v>
+        <v>-0.109</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3028</v>
+        <v>0.5376</v>
       </c>
       <c r="V4" t="n">
         <v>-1.1675</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5089</v>
+        <v>3.2678</v>
       </c>
       <c r="E5" t="n">
-        <v>0.783</v>
+        <v>1.7474</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7259</v>
+        <v>1.5204</v>
       </c>
       <c r="G5" t="n">
         <v>1.7081</v>
@@ -844,13 +844,13 @@
         <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2825</v>
+        <v>1.0414</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8482</v>
+        <v>0.1162</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1307</v>
+        <v>0.9252</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1061</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1562</v>
+        <v>0.5173</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0166</v>
+        <v>0.2309</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1396</v>
+        <v>0.2864</v>
       </c>
       <c r="G6" t="n">
         <v>2.118</v>
@@ -922,13 +922,13 @@
         <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2531</v>
+        <v>0.108</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1305</v>
+        <v>0.0838</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1226</v>
+        <v>0.0242</v>
       </c>
       <c r="V6" t="n">
         <v>-0.4599</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.419</v>
+        <v>-0.4293</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0261</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.393</v>
+        <v>-0.5104</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6017</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1827</v>
+        <v>0.1724</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0419</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2479</v>
+        <v>0.1305</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8572</v>
+        <v>-0.662</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1472</v>
+        <v>-3.0401</v>
       </c>
       <c r="F8" t="n">
-        <v>2.29</v>
+        <v>2.3781</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7096</v>
@@ -1078,13 +1078,13 @@
         <v>2.7055</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2792</v>
+        <v>0.4745</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0743</v>
+        <v>0.1815</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2049</v>
+        <v>0.293</v>
       </c>
       <c r="V8" t="n">
         <v>-0.0106</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>J. BERGENS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9428</v>
+        <v>-0.7214</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0297</v>
+        <v>2.0197</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08699999999999999</v>
+        <v>-2.7411</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.8279</v>
+        <v>1.2635</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.8256</v>
+        <v>1.8465</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9977</v>
+        <v>-0.5829</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.1092</v>
+        <v>2.5046</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.8537</v>
+        <v>2.0915</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7446</v>
+        <v>0.4131</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7187</v>
+        <v>-1.2411</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9719</v>
+        <v>-0.245</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2531</v>
+        <v>-0.996</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8731</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.1624</v>
+        <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2893</v>
+        <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6637</v>
+        <v>0.1755</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6955</v>
+        <v>-0.0281</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.2036</v>
       </c>
       <c r="V9" t="n">
-        <v>2.0945</v>
+        <v>-1.7442</v>
       </c>
       <c r="W9" t="n">
-        <v>4.5463</v>
+        <v>0.5838</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4518</v>
+        <v>-2.328</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BERGENS</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2087</v>
+        <v>-1.2625</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5911</v>
+        <v>-1.7274</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7998</v>
+        <v>0.4649</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2635</v>
+        <v>0.122</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8465</v>
+        <v>0.6846</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5829</v>
+        <v>-0.5625</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5046</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0915</v>
+        <v>0.0192</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4131</v>
+        <v>0.0784</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2411</v>
+        <v>0.0245</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.245</v>
+        <v>0.6654</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.996</v>
+        <v>-0.6409</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4162</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3118</v>
+        <v>0.4885</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4567</v>
+        <v>0.2562</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1449</v>
+        <v>0.2323</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7442</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6133</v>
+        <v>-2.6778</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0489</v>
+        <v>-2.5299</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4355</v>
+        <v>-0.1479</v>
       </c>
       <c r="G11" t="n">
-        <v>0.122</v>
+        <v>-3.8279</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6846</v>
+        <v>-4.8256</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5625</v>
+        <v>0.9977</v>
       </c>
       <c r="J11" t="n">
-        <v>0.09760000000000001</v>
+        <v>-3.1092</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0192</v>
+        <v>-3.8537</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0784</v>
+        <v>0.7446</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0245</v>
+        <v>-0.7187</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6654</v>
+        <v>-0.9719</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6409</v>
+        <v>0.2531</v>
       </c>
       <c r="P11" t="n">
         <v>-1.8731</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0812</v>
+        <v>-4.1624</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2081</v>
+        <v>2.2893</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1377</v>
+        <v>0.9287</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.1953</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2029</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>2.0945</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>4.5463</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.4518</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3142</v>
+        <v>-2.9634</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.718</v>
+        <v>-3.3965</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4038</v>
+        <v>0.4331</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7044</v>
@@ -1390,13 +1390,13 @@
         <v>0.6244</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2662</v>
+        <v>0.0847</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5748</v>
+        <v>-0.2533</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3086</v>
+        <v>0.338</v>
       </c>
       <c r="V12" t="n">
         <v>0.1132</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8058</v>
+        <v>-4.7281</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3783</v>
+        <v>-3.2712</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4275</v>
+        <v>-1.4569</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1718</v>
@@ -1468,13 +1468,13 @@
         <v>1.0406</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3706</v>
+        <v>-0.2928</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5748</v>
+        <v>-0.4676</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2042</v>
+        <v>0.1749</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2229</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.7349</v>
+        <v>13.7346</v>
       </c>
       <c r="E14" t="n">
-        <v>3.012399999999999</v>
+        <v>3.012400000000004</v>
       </c>
       <c r="F14" t="n">
-        <v>10.7223</v>
+        <v>10.7222</v>
       </c>
       <c r="G14" t="n">
         <v>4.530500000000001</v>
@@ -1519,7 +1519,7 @@
         <v>9.797199999999998</v>
       </c>
       <c r="J14" t="n">
-        <v>5.3491</v>
+        <v>5.349100000000002</v>
       </c>
       <c r="K14" t="n">
         <v>-1.57</v>
@@ -1546,16 +1546,16 @@
         <v>18.7307</v>
       </c>
       <c r="S14" t="n">
-        <v>6.243499999999999</v>
+        <v>6.243600000000001</v>
       </c>
       <c r="T14" t="n">
         <v>1.4576</v>
       </c>
       <c r="U14" t="n">
-        <v>4.7859</v>
+        <v>4.786</v>
       </c>
       <c r="V14" t="n">
-        <v>5.041699999999999</v>
+        <v>5.0417</v>
       </c>
       <c r="W14" t="n">
         <v>17.0177</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.9162</v>
+        <v>5.8425</v>
       </c>
       <c r="E15" t="n">
-        <v>7.0211</v>
+        <v>5.9496</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8951</v>
+        <v>-0.1071</v>
       </c>
       <c r="G15" t="n">
         <v>1.8274</v>
@@ -1624,13 +1624,13 @@
         <v>3.3299</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2751</v>
+        <v>1.2014</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9811</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>2.294</v>
+        <v>1.2919</v>
       </c>
       <c r="V15" t="n">
         <v>1.9813</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7421</v>
+        <v>0.9628</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3722</v>
+        <v>0.4794</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3699</v>
+        <v>0.4835</v>
       </c>
       <c r="G16" t="n">
         <v>1.6655</v>
@@ -1702,13 +1702,13 @@
         <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7339</v>
+        <v>-0.5133</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6524</v>
+        <v>-0.5453</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0815</v>
+        <v>0.032</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8137</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3149</v>
+        <v>-0.2856</v>
       </c>
       <c r="E17" t="n">
         <v>-0.2418</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0731</v>
+        <v>-0.0438</v>
       </c>
       <c r="G17" t="n">
         <v>0.3988</v>
@@ -1780,13 +1780,13 @@
         <v>0.4162</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.67</v>
+        <v>-0.6407</v>
       </c>
       <c r="T17" t="n">
         <v>-0.261</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4091</v>
+        <v>-0.3797</v>
       </c>
       <c r="V17" t="n">
         <v>-0.4599</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. MARINA PARRA</t>
+          <t>P. MENDES LIMA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6659</v>
+        <v>-0.4084</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1869</v>
+        <v>-1.3655</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8528</v>
+        <v>0.9571</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1481</v>
+        <v>-1.4489</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3752</v>
+        <v>-0.2087</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5233</v>
+        <v>-1.2401</v>
       </c>
       <c r="J18" t="n">
-        <v>0.305</v>
+        <v>-1.9304</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1875</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1176</v>
+        <v>-1.3504</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4532</v>
+        <v>0.4816</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1877</v>
+        <v>0.3713</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6409</v>
+        <v>0.1102</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8325</v>
+        <v>2.4974</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.4162</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8325</v>
+        <v>2.9137</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1827</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1181</v>
+        <v>-0.8762</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0646</v>
+        <v>-0.103</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1675</v>
+        <v>-0.4776</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.8574</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1675</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. MENDES LIMA</t>
+          <t>N. MARINA PARRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9838</v>
+        <v>-0.5484</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7941</v>
+        <v>0.1869</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8103</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4489</v>
+        <v>-0.1481</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2087</v>
+        <v>0.3752</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2401</v>
+        <v>-0.5233</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.9304</v>
+        <v>0.305</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5800999999999999</v>
+        <v>0.1875</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3504</v>
+        <v>0.1176</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4816</v>
+        <v>-0.4532</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3713</v>
+        <v>0.1877</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1102</v>
+        <v>-0.6409</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4974</v>
+        <v>0.8325</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4162</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9137</v>
+        <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5547</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3049</v>
+        <v>-0.1181</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2498</v>
+        <v>0.0529</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.4776</v>
+        <v>-1.1675</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8574</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3351</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9488</v>
+        <v>-1.5671</v>
       </c>
       <c r="E20" t="n">
         <v>-0.1445</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8043</v>
+        <v>-1.4227</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1129</v>
@@ -2014,13 +2014,13 @@
         <v>3.3299</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2709</v>
+        <v>-0.8892</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3824</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8885</v>
+        <v>-0.5069</v>
       </c>
       <c r="V20" t="n">
         <v>-1.3975</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6305</v>
+        <v>-2.2797</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8365</v>
+        <v>-3.515</v>
       </c>
       <c r="F21" t="n">
-        <v>1.206</v>
+        <v>1.2353</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1069</v>
@@ -2092,13 +2092,13 @@
         <v>1.8731</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8129</v>
+        <v>-0.4621</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9134</v>
+        <v>-0.5919</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1005</v>
+        <v>0.1299</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5838</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2407</v>
+        <v>-3.7074</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9486</v>
+        <v>-2.7343</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2922</v>
+        <v>-0.9731</v>
       </c>
       <c r="G22" t="n">
         <v>0.4057</v>
@@ -2170,13 +2170,13 @@
         <v>2.0812</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5475</v>
+        <v>-1.0142</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7053</v>
+        <v>-0.491</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-0.5232</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6015</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7335</v>
+        <v>-4.7271</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3716</v>
+        <v>-3.4788</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3619</v>
+        <v>-1.2483</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9439</v>
@@ -2248,13 +2248,13 @@
         <v>2.0812</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.852</v>
+        <v>-0.8457</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3824</v>
+        <v>-0.4895</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4697</v>
+        <v>-0.3562</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9376</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.8749</v>
+        <v>-6.3019</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.9654</v>
+        <v>-5.8583</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9095</v>
+        <v>-0.4436</v>
       </c>
       <c r="G24" t="n">
         <v>-1.0673</v>
@@ -2326,13 +2326,13 @@
         <v>3.3299</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.894</v>
+        <v>-1.321</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0472</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8468</v>
+        <v>-0.3809</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5838</v>
@@ -2359,34 +2359,34 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.7347</v>
+        <v>-13.0203</v>
       </c>
       <c r="E25" t="n">
         <v>-10.7223</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.0125</v>
+        <v>-2.2981</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.5306</v>
+        <v>-4.530600000000001</v>
       </c>
       <c r="H25" t="n">
         <v>5.2664</v>
       </c>
       <c r="I25" t="n">
-        <v>-9.797000000000001</v>
+        <v>-9.796999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8183999999999999</v>
+        <v>0.8184000000000003</v>
       </c>
       <c r="K25" t="n">
         <v>3.6963</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.877899999999999</v>
+        <v>-2.8779</v>
       </c>
       <c r="M25" t="n">
-        <v>-5.3491</v>
+        <v>-5.349099999999999</v>
       </c>
       <c r="N25" t="n">
         <v>1.5702</v>
@@ -2404,13 +2404,13 @@
         <v>20.812</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.2435</v>
+        <v>-5.5293</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.786</v>
+        <v>-4.7858</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.4577</v>
+        <v>-0.7431999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-5.0416</v>
